--- a/docassemble/StudentEvaluations/data/sources/massachusetts_educational_evaluations_independent_evaluation_zh-Hans_rev1.xlsx
+++ b/docassemble/StudentEvaluations/data/sources/massachusetts_educational_evaluations_independent_evaluation_zh-Hans_rev1.xlsx
@@ -568,7 +568,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
@@ -612,7 +612,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
@@ -652,7 +652,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
@@ -692,7 +692,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -754,7 +754,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
@@ -1113,7 +1113,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
@@ -1153,7 +1153,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
@@ -1285,7 +1285,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
@@ -1553,7 +1553,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G21" s="4" t="inlineStr">
@@ -1593,7 +1593,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G23" s="4" t="inlineStr">
@@ -1673,7 +1673,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
@@ -1713,7 +1713,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
@@ -1865,7 +1865,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
@@ -1905,7 +1905,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G30" s="4" t="inlineStr">
@@ -1995,7 +1995,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
@@ -2155,7 +2155,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
@@ -2235,7 +2235,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
@@ -2279,7 +2279,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
@@ -2323,7 +2323,7 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
@@ -2365,7 +2365,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
@@ -2407,7 +2407,7 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
@@ -2447,7 +2447,7 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
@@ -2567,7 +2567,7 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
@@ -2607,7 +2607,7 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
@@ -2647,7 +2647,7 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G47" s="3" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G48" s="3" t="inlineStr">
@@ -2731,7 +2731,7 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G49" s="3" t="inlineStr">
@@ -2775,7 +2775,7 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G50" s="3" t="inlineStr">
@@ -2819,7 +2819,7 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G51" s="3" t="inlineStr">
@@ -2859,7 +2859,7 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G52" s="3" t="inlineStr">
@@ -2899,7 +2899,7 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G53" s="3" t="inlineStr">
@@ -2939,7 +2939,7 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G54" s="3" t="inlineStr">
@@ -2985,7 +2985,7 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G55" s="3" t="inlineStr">
@@ -3029,7 +3029,7 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G56" s="3" t="inlineStr">
@@ -3069,7 +3069,7 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G57" s="4" t="inlineStr">
@@ -3109,7 +3109,7 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G58" s="3" t="inlineStr">
@@ -3151,7 +3151,7 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G59" s="3" t="inlineStr">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G60" s="3" t="inlineStr">
@@ -3245,7 +3245,7 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G61" s="3" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G62" s="3" t="inlineStr">
@@ -3339,7 +3339,7 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G63" s="3" t="inlineStr">
@@ -3381,7 +3381,7 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G64" s="3" t="inlineStr">
@@ -3423,7 +3423,7 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G65" s="3" t="inlineStr">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G66" s="3" t="inlineStr">
@@ -3513,7 +3513,7 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G67" s="3" t="inlineStr">
@@ -3557,7 +3557,7 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G68" s="3" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G69" s="3" t="inlineStr">
@@ -3641,7 +3641,7 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G70" s="3" t="inlineStr">
@@ -3683,7 +3683,7 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G71" s="3" t="inlineStr">
@@ -3725,7 +3725,7 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G72" s="3" t="inlineStr">
@@ -3835,7 +3835,7 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G73" s="3" t="inlineStr">
@@ -3877,7 +3877,7 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G74" s="3" t="inlineStr">
@@ -3919,7 +3919,7 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G75" s="3" t="inlineStr">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G76" s="3" t="inlineStr">
@@ -4019,7 +4019,7 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G77" s="3" t="inlineStr">
@@ -4061,7 +4061,7 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G78" s="3" t="inlineStr">
@@ -4103,7 +4103,7 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G79" s="3" t="inlineStr">
@@ -4153,7 +4153,7 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G80" s="4" t="inlineStr">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G81" s="3" t="inlineStr">
@@ -4235,7 +4235,7 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G82" s="3" t="inlineStr">
@@ -4355,7 +4355,7 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G83" s="3" t="inlineStr">
@@ -4395,7 +4395,7 @@
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G84" s="3" t="inlineStr">
@@ -4437,7 +4437,7 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G85" s="3" t="inlineStr">
@@ -4487,7 +4487,7 @@
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G86" s="3" t="inlineStr">
@@ -4527,7 +4527,7 @@
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G87" s="3" t="inlineStr">
@@ -4607,7 +4607,7 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G88" s="3" t="inlineStr">
@@ -4649,7 +4649,7 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G89" s="3" t="inlineStr">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G90" s="3" t="inlineStr">
@@ -4743,7 +4743,7 @@
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G91" s="3" t="inlineStr">
@@ -4785,7 +4785,7 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G92" s="3" t="inlineStr">
@@ -4827,7 +4827,7 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G93" s="3" t="inlineStr">
@@ -4869,7 +4869,7 @@
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G94" s="3" t="inlineStr">
@@ -5039,7 +5039,7 @@
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G95" s="3" t="inlineStr">
@@ -5079,7 +5079,7 @@
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G96" s="3" t="inlineStr">
@@ -5121,7 +5121,7 @@
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G97" s="3" t="inlineStr">
@@ -5163,7 +5163,7 @@
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G98" s="3" t="inlineStr">
@@ -5251,7 +5251,7 @@
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G99" s="3" t="inlineStr">
@@ -5293,7 +5293,7 @@
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G100" s="3" t="inlineStr">
@@ -5333,7 +5333,7 @@
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G101" s="3" t="inlineStr">
@@ -5373,7 +5373,7 @@
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G102" s="3" t="inlineStr">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G103" s="3" t="inlineStr">
@@ -5473,7 +5473,7 @@
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G104" s="3" t="inlineStr">
@@ -5515,7 +5515,7 @@
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G105" s="3" t="inlineStr">
@@ -5555,7 +5555,7 @@
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G106" s="3" t="inlineStr">
@@ -5595,7 +5595,7 @@
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G107" s="3" t="inlineStr">
@@ -5639,7 +5639,7 @@
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G108" s="3" t="inlineStr">
@@ -5679,7 +5679,7 @@
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G109" s="3" t="inlineStr">
@@ -5723,7 +5723,7 @@
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G110" s="3" t="inlineStr">
@@ -5763,7 +5763,7 @@
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G111" s="3" t="inlineStr">
@@ -5811,7 +5811,7 @@
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G112" s="3" t="inlineStr">
@@ -5853,7 +5853,7 @@
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G113" s="3" t="inlineStr">
@@ -5893,7 +5893,7 @@
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G114" s="3" t="inlineStr">
@@ -5933,7 +5933,7 @@
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G115" s="3" t="inlineStr">
@@ -5973,7 +5973,7 @@
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G116" s="3" t="inlineStr">
@@ -6013,7 +6013,7 @@
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G117" s="3" t="inlineStr">
@@ -6053,7 +6053,7 @@
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G118" s="3" t="inlineStr">
@@ -6093,7 +6093,7 @@
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G119" s="3" t="inlineStr">
@@ -6133,7 +6133,7 @@
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G120" s="3" t="inlineStr">
@@ -6173,7 +6173,7 @@
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G121" s="3" t="inlineStr">
@@ -6213,7 +6213,7 @@
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G122" s="3" t="inlineStr">
@@ -6253,7 +6253,7 @@
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G123" s="3" t="inlineStr">
@@ -6293,7 +6293,7 @@
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G124" s="3" t="inlineStr">
@@ -6347,7 +6347,7 @@
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G125" s="3" t="inlineStr">
@@ -6401,7 +6401,7 @@
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G126" s="3" t="inlineStr">
@@ -6443,7 +6443,7 @@
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G127" s="3" t="inlineStr">
@@ -6485,7 +6485,7 @@
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G128" s="3" t="inlineStr">
@@ -6527,7 +6527,7 @@
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G129" s="3" t="inlineStr">
@@ -6569,7 +6569,7 @@
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G130" s="3" t="inlineStr">
@@ -6611,7 +6611,7 @@
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G131" s="3" t="inlineStr">
@@ -6653,7 +6653,7 @@
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G132" s="3" t="inlineStr">
@@ -6695,7 +6695,7 @@
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G133" s="3" t="inlineStr">
@@ -6737,7 +6737,7 @@
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G134" s="3" t="inlineStr">
@@ -6779,7 +6779,7 @@
       </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G135" s="3" t="inlineStr">
@@ -6821,7 +6821,7 @@
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G136" s="3" t="inlineStr">
@@ -6863,7 +6863,7 @@
       </c>
       <c r="F137" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G137" s="3" t="inlineStr">
@@ -6905,7 +6905,7 @@
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G138" s="3" t="inlineStr">
@@ -6947,7 +6947,7 @@
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G139" s="3" t="inlineStr">
@@ -6989,7 +6989,7 @@
       </c>
       <c r="F140" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G140" s="3" t="inlineStr">
@@ -7031,7 +7031,7 @@
       </c>
       <c r="F141" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G141" s="3" t="inlineStr">
@@ -7073,7 +7073,7 @@
       </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G142" s="3" t="inlineStr">
@@ -7115,7 +7115,7 @@
       </c>
       <c r="F143" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G143" s="3" t="inlineStr">
@@ -7157,7 +7157,7 @@
       </c>
       <c r="F144" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G144" s="3" t="inlineStr">
@@ -7199,7 +7199,7 @@
       </c>
       <c r="F145" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G145" s="3" t="inlineStr">
@@ -7241,7 +7241,7 @@
       </c>
       <c r="F146" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G146" s="3" t="inlineStr">
@@ -7285,7 +7285,7 @@
       </c>
       <c r="F147" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G147" s="3" t="inlineStr">
@@ -7335,7 +7335,7 @@
       </c>
       <c r="F148" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G148" s="3" t="inlineStr">
@@ -7377,7 +7377,7 @@
       </c>
       <c r="F149" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G149" s="3" t="inlineStr">
@@ -7419,7 +7419,7 @@
       </c>
       <c r="F150" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G150" s="3" t="inlineStr">
@@ -7461,7 +7461,7 @@
       </c>
       <c r="F151" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G151" s="3" t="inlineStr">
@@ -7503,7 +7503,7 @@
       </c>
       <c r="F152" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G152" s="3" t="inlineStr">
@@ -7545,7 +7545,7 @@
       </c>
       <c r="F153" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G153" s="3" t="inlineStr">
@@ -7587,7 +7587,7 @@
       </c>
       <c r="F154" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G154" s="3" t="inlineStr">
@@ -7629,7 +7629,7 @@
       </c>
       <c r="F155" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G155" s="3" t="inlineStr">
@@ -7679,7 +7679,7 @@
       </c>
       <c r="F156" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G156" s="3" t="inlineStr">
@@ -7725,7 +7725,7 @@
       </c>
       <c r="F157" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G157" s="3" t="inlineStr">
@@ -7777,7 +7777,7 @@
       </c>
       <c r="F158" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G158" s="3" t="inlineStr">
@@ -7819,7 +7819,7 @@
       </c>
       <c r="F159" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G159" s="3" t="inlineStr">
@@ -7859,7 +7859,7 @@
       </c>
       <c r="F160" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G160" s="3" t="inlineStr">
@@ -7901,7 +7901,7 @@
       </c>
       <c r="F161" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G161" s="3" t="inlineStr">
@@ -7943,7 +7943,7 @@
       </c>
       <c r="F162" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G162" s="3" t="inlineStr">
@@ -7985,7 +7985,7 @@
       </c>
       <c r="F163" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G163" s="3" t="inlineStr">
@@ -8027,7 +8027,7 @@
       </c>
       <c r="F164" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G164" s="3" t="inlineStr">
@@ -8067,7 +8067,7 @@
       </c>
       <c r="F165" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G165" s="3" t="inlineStr">
@@ -8109,7 +8109,7 @@
       </c>
       <c r="F166" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G166" s="4" t="inlineStr">
@@ -8149,7 +8149,7 @@
       </c>
       <c r="F167" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G167" s="4" t="inlineStr">
@@ -8189,7 +8189,7 @@
       </c>
       <c r="F168" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G168" s="4" t="inlineStr">
@@ -8229,7 +8229,7 @@
       </c>
       <c r="F169" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G169" s="4" t="inlineStr">
@@ -8269,7 +8269,7 @@
       </c>
       <c r="F170" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G170" s="4" t="inlineStr">
@@ -8309,7 +8309,7 @@
       </c>
       <c r="F171" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G171" s="4" t="inlineStr">
@@ -8349,7 +8349,7 @@
       </c>
       <c r="F172" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G172" s="4" t="inlineStr">
@@ -8389,7 +8389,7 @@
       </c>
       <c r="F173" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G173" s="4" t="inlineStr">
@@ -8429,7 +8429,7 @@
       </c>
       <c r="F174" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G174" s="3" t="inlineStr">
@@ -8471,7 +8471,7 @@
       </c>
       <c r="F175" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G175" s="3" t="inlineStr">
@@ -8511,7 +8511,7 @@
       </c>
       <c r="F176" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G176" s="4" t="inlineStr">
@@ -8551,7 +8551,7 @@
       </c>
       <c r="F177" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G177" s="4" t="inlineStr">
@@ -8591,7 +8591,7 @@
       </c>
       <c r="F178" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G178" s="4" t="inlineStr">
@@ -8631,7 +8631,7 @@
       </c>
       <c r="F179" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G179" s="4" t="inlineStr">
@@ -8671,7 +8671,7 @@
       </c>
       <c r="F180" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G180" s="4" t="inlineStr">
@@ -8711,7 +8711,7 @@
       </c>
       <c r="F181" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G181" s="3" t="inlineStr">
@@ -8753,7 +8753,7 @@
       </c>
       <c r="F182" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G182" s="3" t="inlineStr">
@@ -8793,7 +8793,7 @@
       </c>
       <c r="F183" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G183" s="4" t="inlineStr">
@@ -8833,7 +8833,7 @@
       </c>
       <c r="F184" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G184" s="4" t="inlineStr">
@@ -8873,7 +8873,7 @@
       </c>
       <c r="F185" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G185" s="4" t="inlineStr">
@@ -8913,7 +8913,7 @@
       </c>
       <c r="F186" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G186" s="4" t="inlineStr">
@@ -8953,7 +8953,7 @@
       </c>
       <c r="F187" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G187" s="4" t="inlineStr">
@@ -8993,7 +8993,7 @@
       </c>
       <c r="F188" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G188" s="4" t="inlineStr">
@@ -9033,7 +9033,7 @@
       </c>
       <c r="F189" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G189" s="3" t="inlineStr">
@@ -9075,7 +9075,7 @@
       </c>
       <c r="F190" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G190" s="3" t="inlineStr">
@@ -9115,7 +9115,7 @@
       </c>
       <c r="F191" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G191" s="4" t="inlineStr">
@@ -9155,7 +9155,7 @@
       </c>
       <c r="F192" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G192" s="4" t="inlineStr">
@@ -9195,7 +9195,7 @@
       </c>
       <c r="F193" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G193" s="4" t="inlineStr">
@@ -9235,7 +9235,7 @@
       </c>
       <c r="F194" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G194" s="4" t="inlineStr">
@@ -9275,7 +9275,7 @@
       </c>
       <c r="F195" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G195" s="4" t="inlineStr">
@@ -9315,7 +9315,7 @@
       </c>
       <c r="F196" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G196" s="4" t="inlineStr">
@@ -9355,7 +9355,7 @@
       </c>
       <c r="F197" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G197" s="3" t="inlineStr">
@@ -9397,7 +9397,7 @@
       </c>
       <c r="F198" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G198" s="3" t="inlineStr">
@@ -9437,7 +9437,7 @@
       </c>
       <c r="F199" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G199" s="3" t="inlineStr">
@@ -9477,7 +9477,7 @@
       </c>
       <c r="F200" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G200" s="3" t="inlineStr">
@@ -9517,7 +9517,7 @@
       </c>
       <c r="F201" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G201" s="3" t="inlineStr">
@@ -9557,7 +9557,7 @@
       </c>
       <c r="F202" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G202" s="3" t="inlineStr">
@@ -9597,7 +9597,7 @@
       </c>
       <c r="F203" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G203" s="3" t="inlineStr">
@@ -9637,7 +9637,7 @@
       </c>
       <c r="F204" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G204" s="3" t="inlineStr">
@@ -9677,7 +9677,7 @@
       </c>
       <c r="F205" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G205" s="3" t="inlineStr">
@@ -9717,7 +9717,7 @@
       </c>
       <c r="F206" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G206" s="3" t="inlineStr">
@@ -9757,7 +9757,7 @@
       </c>
       <c r="F207" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G207" s="3" t="inlineStr">
@@ -9797,7 +9797,7 @@
       </c>
       <c r="F208" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G208" s="3" t="inlineStr">
@@ -9837,7 +9837,7 @@
       </c>
       <c r="F209" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G209" s="3" t="inlineStr">
@@ -9877,7 +9877,7 @@
       </c>
       <c r="F210" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G210" s="3" t="inlineStr">
@@ -9917,7 +9917,7 @@
       </c>
       <c r="F211" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G211" s="3" t="inlineStr">
@@ -9957,7 +9957,7 @@
       </c>
       <c r="F212" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G212" s="3" t="inlineStr">
@@ -9997,7 +9997,7 @@
       </c>
       <c r="F213" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G213" s="3" t="inlineStr">
@@ -10037,7 +10037,7 @@
       </c>
       <c r="F214" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G214" s="3" t="inlineStr">
@@ -10077,7 +10077,7 @@
       </c>
       <c r="F215" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G215" s="3" t="inlineStr">
@@ -10119,7 +10119,7 @@
       </c>
       <c r="F216" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G216" s="3" t="inlineStr">
@@ -10163,7 +10163,7 @@
       </c>
       <c r="F217" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G217" s="3" t="inlineStr">
@@ -10203,7 +10203,7 @@
       </c>
       <c r="F218" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G218" s="3" t="inlineStr">
@@ -10243,7 +10243,7 @@
       </c>
       <c r="F219" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G219" s="3" t="inlineStr">
@@ -10283,7 +10283,7 @@
       </c>
       <c r="F220" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G220" s="3" t="inlineStr">
@@ -10323,7 +10323,7 @@
       </c>
       <c r="F221" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G221" s="3" t="inlineStr">
@@ -10371,7 +10371,7 @@
       </c>
       <c r="F222" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G222" s="3" t="inlineStr">
@@ -10429,7 +10429,7 @@
       </c>
       <c r="F223" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G223" s="3" t="inlineStr">
@@ -10471,7 +10471,7 @@
       </c>
       <c r="F224" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G224" s="3" t="inlineStr">
@@ -10513,7 +10513,7 @@
       </c>
       <c r="F225" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G225" s="3" t="inlineStr">
@@ -10553,7 +10553,7 @@
       </c>
       <c r="F226" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G226" s="3" t="inlineStr">
@@ -10593,7 +10593,7 @@
       </c>
       <c r="F227" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G227" s="3" t="inlineStr">
@@ -10635,7 +10635,7 @@
       </c>
       <c r="F228" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G228" s="3" t="inlineStr">
@@ -10675,7 +10675,7 @@
       </c>
       <c r="F229" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G229" s="3" t="inlineStr">
@@ -10717,7 +10717,7 @@
       </c>
       <c r="F230" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G230" s="3" t="inlineStr">
@@ -10761,7 +10761,7 @@
       </c>
       <c r="F231" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G231" s="3" t="inlineStr">
@@ -10803,7 +10803,7 @@
       </c>
       <c r="F232" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G232" s="3" t="inlineStr">
@@ -10845,7 +10845,7 @@
       </c>
       <c r="F233" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G233" s="3" t="inlineStr">
@@ -10887,7 +10887,7 @@
       </c>
       <c r="F234" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G234" s="3" t="inlineStr">
@@ -10929,7 +10929,7 @@
       </c>
       <c r="F235" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G235" s="3" t="inlineStr">
@@ -10971,7 +10971,7 @@
       </c>
       <c r="F236" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G236" s="3" t="inlineStr">
@@ -11021,7 +11021,7 @@
       </c>
       <c r="F237" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G237" s="3" t="inlineStr">
@@ -11061,7 +11061,7 @@
       </c>
       <c r="F238" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G238" s="3" t="inlineStr">
@@ -11111,7 +11111,7 @@
       </c>
       <c r="F239" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G239" s="3" t="inlineStr">
@@ -11153,7 +11153,7 @@
       </c>
       <c r="F240" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G240" s="3" t="inlineStr">
@@ -11203,7 +11203,7 @@
       </c>
       <c r="F241" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G241" s="3" t="inlineStr">
@@ -11245,7 +11245,7 @@
       </c>
       <c r="F242" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G242" s="3" t="inlineStr">
@@ -11296,7 +11296,7 @@
       </c>
       <c r="F243" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G243" s="3" t="inlineStr">
@@ -11338,7 +11338,7 @@
       </c>
       <c r="F244" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G244" s="3" t="inlineStr">
@@ -11390,7 +11390,7 @@
       </c>
       <c r="F245" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G245" s="3" t="inlineStr">
@@ -11442,7 +11442,7 @@
       </c>
       <c r="F246" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G246" s="3" t="inlineStr">
@@ -11484,7 +11484,7 @@
       </c>
       <c r="F247" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G247" s="3" t="inlineStr">
@@ -11526,7 +11526,7 @@
       </c>
       <c r="F248" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G248" s="3" t="inlineStr">
@@ -11568,7 +11568,7 @@
       </c>
       <c r="F249" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G249" s="3" t="inlineStr">
@@ -11608,7 +11608,7 @@
       </c>
       <c r="F250" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G250" s="3" t="inlineStr">
@@ -11650,7 +11650,7 @@
       </c>
       <c r="F251" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G251" s="3" t="inlineStr">
@@ -11698,7 +11698,7 @@
       </c>
       <c r="F252" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G252" s="3" t="inlineStr">
@@ -11740,7 +11740,7 @@
       </c>
       <c r="F253" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G253" s="3" t="inlineStr">
@@ -11788,7 +11788,7 @@
       </c>
       <c r="F254" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G254" s="3" t="inlineStr">
@@ -11828,7 +11828,7 @@
       </c>
       <c r="F255" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G255" s="3" t="inlineStr">
@@ -11870,7 +11870,7 @@
       </c>
       <c r="F256" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G256" s="3" t="inlineStr">
@@ -11910,7 +11910,7 @@
       </c>
       <c r="F257" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G257" s="3" t="inlineStr">
@@ -11952,7 +11952,7 @@
       </c>
       <c r="F258" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G258" s="3" t="inlineStr">
@@ -12000,7 +12000,7 @@
       </c>
       <c r="F259" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G259" s="3" t="inlineStr">
@@ -12042,7 +12042,7 @@
       </c>
       <c r="F260" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G260" s="3" t="inlineStr">
@@ -12090,7 +12090,7 @@
       </c>
       <c r="F261" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G261" s="3" t="inlineStr">
@@ -12130,7 +12130,7 @@
       </c>
       <c r="F262" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G262" s="3" t="inlineStr">
@@ -12172,7 +12172,7 @@
       </c>
       <c r="F263" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G263" s="3" t="inlineStr">
@@ -12212,7 +12212,7 @@
       </c>
       <c r="F264" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G264" s="3" t="inlineStr">
@@ -12254,7 +12254,7 @@
       </c>
       <c r="F265" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G265" s="3" t="inlineStr">
@@ -12302,7 +12302,7 @@
       </c>
       <c r="F266" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G266" s="3" t="inlineStr">
@@ -12344,7 +12344,7 @@
       </c>
       <c r="F267" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G267" s="3" t="inlineStr">
@@ -12392,7 +12392,7 @@
       </c>
       <c r="F268" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G268" s="3" t="inlineStr">
@@ -12432,7 +12432,7 @@
       </c>
       <c r="F269" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G269" s="3" t="inlineStr">
@@ -12474,7 +12474,7 @@
       </c>
       <c r="F270" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G270" s="3" t="inlineStr">
@@ -12514,7 +12514,7 @@
       </c>
       <c r="F271" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G271" s="3" t="inlineStr">
@@ -12556,7 +12556,7 @@
       </c>
       <c r="F272" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G272" s="3" t="inlineStr">
@@ -12604,7 +12604,7 @@
       </c>
       <c r="F273" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G273" s="3" t="inlineStr">
@@ -12646,7 +12646,7 @@
       </c>
       <c r="F274" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G274" s="3" t="inlineStr">
@@ -12694,7 +12694,7 @@
       </c>
       <c r="F275" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G275" s="3" t="inlineStr">
@@ -12734,7 +12734,7 @@
       </c>
       <c r="F276" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G276" s="3" t="inlineStr">
@@ -12776,7 +12776,7 @@
       </c>
       <c r="F277" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G277" s="3" t="inlineStr">
@@ -12816,7 +12816,7 @@
       </c>
       <c r="F278" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G278" s="3" t="inlineStr">
@@ -12858,7 +12858,7 @@
       </c>
       <c r="F279" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G279" s="3" t="inlineStr">
@@ -12898,7 +12898,7 @@
       </c>
       <c r="F280" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G280" s="3" t="inlineStr">
@@ -12940,7 +12940,7 @@
       </c>
       <c r="F281" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G281" s="3" t="inlineStr">
@@ -12982,7 +12982,7 @@
       </c>
       <c r="F282" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G282" s="3" t="inlineStr">
@@ -13024,7 +13024,7 @@
       </c>
       <c r="F283" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G283" s="3" t="inlineStr">
@@ -13064,7 +13064,7 @@
       </c>
       <c r="F284" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G284" s="3" t="inlineStr">
@@ -13110,7 +13110,7 @@
       </c>
       <c r="F285" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G285" s="3" t="inlineStr">
@@ -13152,7 +13152,7 @@
       </c>
       <c r="F286" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G286" s="3" t="inlineStr">
@@ -13194,7 +13194,7 @@
       </c>
       <c r="F287" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G287" s="3" t="inlineStr">
@@ -13236,7 +13236,7 @@
       </c>
       <c r="F288" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G288" s="3" t="inlineStr">
@@ -13278,7 +13278,7 @@
       </c>
       <c r="F289" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G289" s="3" t="inlineStr">
@@ -13320,7 +13320,7 @@
       </c>
       <c r="F290" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G290" s="3" t="inlineStr">
@@ -13360,7 +13360,7 @@
       </c>
       <c r="F291" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G291" s="4" t="inlineStr">
@@ -13400,7 +13400,7 @@
       </c>
       <c r="F292" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G292" s="3" t="inlineStr">
@@ -13442,7 +13442,7 @@
       </c>
       <c r="F293" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G293" s="3" t="inlineStr">
@@ -13484,7 +13484,7 @@
       </c>
       <c r="F294" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G294" s="3" t="inlineStr">
@@ -13536,7 +13536,7 @@
       </c>
       <c r="F295" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G295" s="3" t="inlineStr">
@@ -13576,7 +13576,7 @@
       </c>
       <c r="F296" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G296" s="3" t="inlineStr">
@@ -13616,7 +13616,7 @@
       </c>
       <c r="F297" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G297" s="3" t="inlineStr">
@@ -13658,7 +13658,7 @@
       </c>
       <c r="F298" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G298" s="3" t="inlineStr">
@@ -13706,7 +13706,7 @@
       </c>
       <c r="F299" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G299" s="3" t="inlineStr">
@@ -13746,7 +13746,7 @@
       </c>
       <c r="F300" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G300" s="3" t="inlineStr">
@@ -13786,7 +13786,7 @@
       </c>
       <c r="F301" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G301" s="3" t="inlineStr">
@@ -13828,7 +13828,7 @@
       </c>
       <c r="F302" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G302" s="3" t="inlineStr">
@@ -13868,7 +13868,7 @@
       </c>
       <c r="F303" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G303" s="3" t="inlineStr">
@@ -13908,7 +13908,7 @@
       </c>
       <c r="F304" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G304" s="3" t="inlineStr">
@@ -13948,7 +13948,7 @@
       </c>
       <c r="F305" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G305" s="3" t="inlineStr">
@@ -13988,7 +13988,7 @@
       </c>
       <c r="F306" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G306" s="3" t="inlineStr">
@@ -14028,7 +14028,7 @@
       </c>
       <c r="F307" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G307" s="3" t="inlineStr">
@@ -14068,7 +14068,7 @@
       </c>
       <c r="F308" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G308" s="3" t="inlineStr">
@@ -14110,7 +14110,7 @@
       </c>
       <c r="F309" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G309" s="3" t="inlineStr">
@@ -14150,7 +14150,7 @@
       </c>
       <c r="F310" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G310" s="3" t="inlineStr">
@@ -14192,7 +14192,7 @@
       </c>
       <c r="F311" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G311" s="3" t="inlineStr">
@@ -14232,7 +14232,7 @@
       </c>
       <c r="F312" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G312" s="3" t="inlineStr">
@@ -14274,7 +14274,7 @@
       </c>
       <c r="F313" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G313" s="3" t="inlineStr">
@@ -14314,7 +14314,7 @@
       </c>
       <c r="F314" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G314" s="3" t="inlineStr">
@@ -14376,7 +14376,7 @@
       </c>
       <c r="F315" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G315" s="3" t="inlineStr">
@@ -14418,7 +14418,7 @@
       </c>
       <c r="F316" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G316" s="3" t="inlineStr">
@@ -14472,7 +14472,7 @@
       </c>
       <c r="F317" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G317" s="3" t="inlineStr">
@@ -14520,7 +14520,7 @@
       </c>
       <c r="F318" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G318" s="3" t="inlineStr">
@@ -14560,7 +14560,7 @@
       </c>
       <c r="F319" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G319" s="3" t="inlineStr">
@@ -14600,7 +14600,7 @@
       </c>
       <c r="F320" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G320" s="3" t="inlineStr">
@@ -14640,7 +14640,7 @@
       </c>
       <c r="F321" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G321" s="3" t="inlineStr">
@@ -14680,7 +14680,7 @@
       </c>
       <c r="F322" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G322" s="3" t="inlineStr">
@@ -14720,7 +14720,7 @@
       </c>
       <c r="F323" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G323" s="3" t="inlineStr">
@@ -14760,7 +14760,7 @@
       </c>
       <c r="F324" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G324" s="3" t="inlineStr">
@@ -14802,7 +14802,7 @@
       </c>
       <c r="F325" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G325" s="3" t="inlineStr">
@@ -14848,7 +14848,7 @@
       </c>
       <c r="F326" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G326" s="3" t="inlineStr">
@@ -14890,7 +14890,7 @@
       </c>
       <c r="F327" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G327" s="3" t="inlineStr">
@@ -14932,7 +14932,7 @@
       </c>
       <c r="F328" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G328" s="3" t="inlineStr">
@@ -14972,7 +14972,7 @@
       </c>
       <c r="F329" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G329" s="3" t="inlineStr">
@@ -15014,7 +15014,7 @@
       </c>
       <c r="F330" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G330" s="3" t="inlineStr">
@@ -15054,7 +15054,7 @@
       </c>
       <c r="F331" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G331" s="3" t="inlineStr">
@@ -15094,7 +15094,7 @@
       </c>
       <c r="F332" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G332" s="3" t="inlineStr">
@@ -15134,7 +15134,7 @@
       </c>
       <c r="F333" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G333" s="3" t="inlineStr">
@@ -15184,7 +15184,7 @@
       </c>
       <c r="F334" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G334" s="3" t="inlineStr">
@@ -15249,7 +15249,7 @@
       </c>
       <c r="F335" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G335" s="3" t="inlineStr">
@@ -15291,7 +15291,7 @@
       </c>
       <c r="F336" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G336" s="3" t="inlineStr">
@@ -15347,7 +15347,7 @@
       </c>
       <c r="F337" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G337" s="3" t="inlineStr">
@@ -15387,7 +15387,7 @@
       </c>
       <c r="F338" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G338" s="3" t="inlineStr">
@@ -15427,7 +15427,7 @@
       </c>
       <c r="F339" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G339" s="4" t="inlineStr">
@@ -15467,7 +15467,7 @@
       </c>
       <c r="F340" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G340" s="3" t="inlineStr">
@@ -15509,7 +15509,7 @@
       </c>
       <c r="F341" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G341" s="3" t="inlineStr">
@@ -15557,7 +15557,7 @@
       </c>
       <c r="F342" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G342" s="3" t="inlineStr">
@@ -15599,7 +15599,7 @@
       </c>
       <c r="F343" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G343" s="3" t="inlineStr">
@@ -15641,7 +15641,7 @@
       </c>
       <c r="F344" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G344" s="3" t="inlineStr">
@@ -15685,7 +15685,7 @@
       </c>
       <c r="F345" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G345" s="3" t="inlineStr">
@@ -15731,7 +15731,7 @@
       </c>
       <c r="F346" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G346" s="3" t="inlineStr">
@@ -15773,7 +15773,7 @@
       </c>
       <c r="F347" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G347" s="3" t="inlineStr">
@@ -15829,7 +15829,7 @@
       </c>
       <c r="F348" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G348" s="3" t="inlineStr">
@@ -15869,7 +15869,7 @@
       </c>
       <c r="F349" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G349" s="3" t="inlineStr">
@@ -15923,7 +15923,7 @@
       </c>
       <c r="F350" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G350" s="3" t="inlineStr">
@@ -15965,7 +15965,7 @@
       </c>
       <c r="F351" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G351" s="3" t="inlineStr">
@@ -16005,7 +16005,7 @@
       </c>
       <c r="F352" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G352" s="3" t="inlineStr">
@@ -16047,7 +16047,7 @@
       </c>
       <c r="F353" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G353" s="3" t="inlineStr">
@@ -16119,7 +16119,7 @@
       </c>
       <c r="F354" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G354" s="3" t="inlineStr">
@@ -16159,7 +16159,7 @@
       </c>
       <c r="F355" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G355" s="4" t="inlineStr">
@@ -16199,7 +16199,7 @@
       </c>
       <c r="F356" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G356" s="3" t="inlineStr">
@@ -16239,7 +16239,7 @@
       </c>
       <c r="F357" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G357" s="3" t="inlineStr">
@@ -16289,7 +16289,7 @@
       </c>
       <c r="F358" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G358" s="3" t="inlineStr">
@@ -16355,7 +16355,7 @@
       </c>
       <c r="F359" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G359" s="3" t="inlineStr">
@@ -16425,7 +16425,7 @@
       </c>
       <c r="F360" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G360" s="3" t="inlineStr">
@@ -16467,7 +16467,7 @@
       </c>
       <c r="F361" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G361" s="3" t="inlineStr">
@@ -16509,7 +16509,7 @@
       </c>
       <c r="F362" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G362" s="3" t="inlineStr">
@@ -16573,7 +16573,7 @@
       </c>
       <c r="F363" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G363" s="4" t="inlineStr">
@@ -16613,7 +16613,7 @@
       </c>
       <c r="F364" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G364" s="3" t="inlineStr">
@@ -16657,7 +16657,7 @@
       </c>
       <c r="F365" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G365" s="3" t="inlineStr">
@@ -16707,7 +16707,7 @@
       </c>
       <c r="F366" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G366" s="3" t="inlineStr">
@@ -16747,7 +16747,7 @@
       </c>
       <c r="F367" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G367" s="3" t="inlineStr">
@@ -16791,7 +16791,7 @@
       </c>
       <c r="F368" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G368" s="3" t="inlineStr">
@@ -16831,7 +16831,7 @@
       </c>
       <c r="F369" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G369" s="3" t="inlineStr">
@@ -16871,7 +16871,7 @@
       </c>
       <c r="F370" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G370" s="3" t="inlineStr">
@@ -16913,7 +16913,7 @@
       </c>
       <c r="F371" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G371" s="3" t="inlineStr">
@@ -16955,7 +16955,7 @@
       </c>
       <c r="F372" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G372" s="3" t="inlineStr">
@@ -16995,7 +16995,7 @@
       </c>
       <c r="F373" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G373" s="3" t="inlineStr">
@@ -17035,7 +17035,7 @@
       </c>
       <c r="F374" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G374" s="3" t="inlineStr">
@@ -17077,7 +17077,7 @@
       </c>
       <c r="F375" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G375" s="3" t="inlineStr">
@@ -17129,7 +17129,7 @@
       </c>
       <c r="F376" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G376" s="3" t="inlineStr">
@@ -17169,7 +17169,7 @@
       </c>
       <c r="F377" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G377" s="3" t="inlineStr">
@@ -17209,7 +17209,7 @@
       </c>
       <c r="F378" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G378" s="3" t="inlineStr">
@@ -17253,7 +17253,7 @@
       </c>
       <c r="F379" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G379" s="3" t="inlineStr">
@@ -17295,7 +17295,7 @@
       </c>
       <c r="F380" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G380" s="3" t="inlineStr">
@@ -17337,7 +17337,7 @@
       </c>
       <c r="F381" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G381" s="3" t="inlineStr">
@@ -17377,7 +17377,7 @@
       </c>
       <c r="F382" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G382" s="3" t="inlineStr">
@@ -17421,7 +17421,7 @@
       </c>
       <c r="F383" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G383" s="3" t="inlineStr">
@@ -17471,7 +17471,7 @@
       </c>
       <c r="F384" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G384" s="3" t="inlineStr">
@@ -17511,7 +17511,7 @@
       </c>
       <c r="F385" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G385" s="3" t="inlineStr">
@@ -17551,7 +17551,7 @@
       </c>
       <c r="F386" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G386" s="3" t="inlineStr">
@@ -17593,7 +17593,7 @@
       </c>
       <c r="F387" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G387" s="3" t="inlineStr">
@@ -17635,7 +17635,7 @@
       </c>
       <c r="F388" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G388" s="4" t="inlineStr">
@@ -17675,7 +17675,7 @@
       </c>
       <c r="F389" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G389" s="4" t="inlineStr">
@@ -17715,7 +17715,7 @@
       </c>
       <c r="F390" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G390" s="4" t="inlineStr">
@@ -17755,7 +17755,7 @@
       </c>
       <c r="F391" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G391" s="3" t="inlineStr">
@@ -17797,7 +17797,7 @@
       </c>
       <c r="F392" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G392" s="3" t="inlineStr">
@@ -17839,7 +17839,7 @@
       </c>
       <c r="F393" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G393" s="3" t="inlineStr">
@@ -17881,7 +17881,7 @@
       </c>
       <c r="F394" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G394" s="3" t="inlineStr">
@@ -17923,7 +17923,7 @@
       </c>
       <c r="F395" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G395" s="3" t="inlineStr">
@@ -17975,7 +17975,7 @@
       </c>
       <c r="F396" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G396" s="3" t="inlineStr">
@@ -18017,7 +18017,7 @@
       </c>
       <c r="F397" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G397" s="3" t="inlineStr">
@@ -18061,7 +18061,7 @@
       </c>
       <c r="F398" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G398" s="3" t="inlineStr">
@@ -18103,7 +18103,7 @@
       </c>
       <c r="F399" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G399" s="3" t="inlineStr">
@@ -18143,7 +18143,7 @@
       </c>
       <c r="F400" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G400" s="3" t="inlineStr">
@@ -18183,7 +18183,7 @@
       </c>
       <c r="F401" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G401" s="3" t="inlineStr">
@@ -18223,7 +18223,7 @@
       </c>
       <c r="F402" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G402" s="3" t="inlineStr">
@@ -18263,7 +18263,7 @@
       </c>
       <c r="F403" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G403" s="3" t="inlineStr">
@@ -18303,7 +18303,7 @@
       </c>
       <c r="F404" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G404" s="3" t="inlineStr">
@@ -18343,7 +18343,7 @@
       </c>
       <c r="F405" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G405" s="3" t="inlineStr">
@@ -18383,7 +18383,7 @@
       </c>
       <c r="F406" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G406" s="3" t="inlineStr">
@@ -18423,7 +18423,7 @@
       </c>
       <c r="F407" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G407" s="3" t="inlineStr">
@@ -18463,7 +18463,7 @@
       </c>
       <c r="F408" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G408" s="3" t="inlineStr">
@@ -18503,7 +18503,7 @@
       </c>
       <c r="F409" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G409" s="3" t="inlineStr">
@@ -18543,7 +18543,7 @@
       </c>
       <c r="F410" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G410" s="3" t="inlineStr">
@@ -18583,7 +18583,7 @@
       </c>
       <c r="F411" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G411" s="3" t="inlineStr">
@@ -18625,7 +18625,7 @@
       </c>
       <c r="F412" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G412" s="3" t="inlineStr">
@@ -18667,7 +18667,7 @@
       </c>
       <c r="F413" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G413" s="3" t="inlineStr">
@@ -18709,7 +18709,7 @@
       </c>
       <c r="F414" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G414" s="3" t="inlineStr">
@@ -18751,7 +18751,7 @@
       </c>
       <c r="F415" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G415" s="3" t="inlineStr">
@@ -18793,7 +18793,7 @@
       </c>
       <c r="F416" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G416" s="3" t="inlineStr">
@@ -18835,7 +18835,7 @@
       </c>
       <c r="F417" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G417" s="3" t="inlineStr">
@@ -18877,7 +18877,7 @@
       </c>
       <c r="F418" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G418" s="3" t="inlineStr">
@@ -18919,7 +18919,7 @@
       </c>
       <c r="F419" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G419" s="3" t="inlineStr">
@@ -18961,7 +18961,7 @@
       </c>
       <c r="F420" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G420" s="3" t="inlineStr">
@@ -19001,7 +19001,7 @@
       </c>
       <c r="F421" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G421" s="3" t="inlineStr">
@@ -19041,7 +19041,7 @@
       </c>
       <c r="F422" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G422" s="3" t="inlineStr">
@@ -19081,7 +19081,7 @@
       </c>
       <c r="F423" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G423" s="3" t="inlineStr">
@@ -19121,7 +19121,7 @@
       </c>
       <c r="F424" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G424" s="3" t="inlineStr">
@@ -19163,7 +19163,7 @@
       </c>
       <c r="F425" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G425" s="3" t="inlineStr">
@@ -19205,7 +19205,7 @@
       </c>
       <c r="F426" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G426" s="3" t="inlineStr">
@@ -19247,7 +19247,7 @@
       </c>
       <c r="F427" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G427" s="3" t="inlineStr">
@@ -19289,7 +19289,7 @@
       </c>
       <c r="F428" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G428" s="3" t="inlineStr">
@@ -19331,7 +19331,7 @@
       </c>
       <c r="F429" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G429" s="3" t="inlineStr">
@@ -19373,7 +19373,7 @@
       </c>
       <c r="F430" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G430" s="3" t="inlineStr">
@@ -19415,7 +19415,7 @@
       </c>
       <c r="F431" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G431" s="3" t="inlineStr">
@@ -19457,7 +19457,7 @@
       </c>
       <c r="F432" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G432" s="3" t="inlineStr">
@@ -19499,7 +19499,7 @@
       </c>
       <c r="F433" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G433" s="3" t="inlineStr">
@@ -19541,7 +19541,7 @@
       </c>
       <c r="F434" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G434" s="3" t="inlineStr">
@@ -19583,7 +19583,7 @@
       </c>
       <c r="F435" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G435" s="3" t="inlineStr">
@@ -19625,7 +19625,7 @@
       </c>
       <c r="F436" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G436" s="3" t="inlineStr">
@@ -19667,7 +19667,7 @@
       </c>
       <c r="F437" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G437" s="3" t="inlineStr">
@@ -19709,7 +19709,7 @@
       </c>
       <c r="F438" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G438" s="3" t="inlineStr">
@@ -19751,7 +19751,7 @@
       </c>
       <c r="F439" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G439" s="3" t="inlineStr">
@@ -19793,7 +19793,7 @@
       </c>
       <c r="F440" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G440" s="3" t="inlineStr">
@@ -19835,7 +19835,7 @@
       </c>
       <c r="F441" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G441" s="3" t="inlineStr">
@@ -19877,7 +19877,7 @@
       </c>
       <c r="F442" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G442" s="3" t="inlineStr">
@@ -19919,7 +19919,7 @@
       </c>
       <c r="F443" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G443" s="3" t="inlineStr">
@@ -19961,7 +19961,7 @@
       </c>
       <c r="F444" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G444" s="3" t="inlineStr">
@@ -20003,7 +20003,7 @@
       </c>
       <c r="F445" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G445" s="3" t="inlineStr">
@@ -20045,7 +20045,7 @@
       </c>
       <c r="F446" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G446" s="3" t="inlineStr">
@@ -20087,7 +20087,7 @@
       </c>
       <c r="F447" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G447" s="3" t="inlineStr">
@@ -20129,7 +20129,7 @@
       </c>
       <c r="F448" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G448" s="3" t="inlineStr">
@@ -20173,7 +20173,7 @@
       </c>
       <c r="F449" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G449" s="3" t="inlineStr">
@@ -20215,7 +20215,7 @@
       </c>
       <c r="F450" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G450" s="3" t="inlineStr">
@@ -20257,7 +20257,7 @@
       </c>
       <c r="F451" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G451" s="3" t="inlineStr">
@@ -20299,7 +20299,7 @@
       </c>
       <c r="F452" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G452" s="3" t="inlineStr">
@@ -20341,7 +20341,7 @@
       </c>
       <c r="F453" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G453" s="3" t="inlineStr">
@@ -20383,7 +20383,7 @@
       </c>
       <c r="F454" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G454" s="3" t="inlineStr">
@@ -20425,7 +20425,7 @@
       </c>
       <c r="F455" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G455" s="3" t="inlineStr">
@@ -20467,7 +20467,7 @@
       </c>
       <c r="F456" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G456" s="3" t="inlineStr">
@@ -20509,7 +20509,7 @@
       </c>
       <c r="F457" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G457" s="3" t="inlineStr">
@@ -20549,7 +20549,7 @@
       </c>
       <c r="F458" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G458" s="3" t="inlineStr">
@@ -20589,7 +20589,7 @@
       </c>
       <c r="F459" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G459" s="3" t="inlineStr">
@@ -20629,7 +20629,7 @@
       </c>
       <c r="F460" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G460" s="3" t="inlineStr">
@@ -20669,7 +20669,7 @@
       </c>
       <c r="F461" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G461" s="3" t="inlineStr">
@@ -20713,7 +20713,7 @@
       </c>
       <c r="F462" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G462" s="3" t="inlineStr">
@@ -20787,7 +20787,7 @@
       </c>
       <c r="F463" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G463" s="3" t="inlineStr">
@@ -20829,7 +20829,7 @@
       </c>
       <c r="F464" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G464" s="3" t="inlineStr">
@@ -20871,7 +20871,7 @@
       </c>
       <c r="F465" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G465" s="3" t="inlineStr">
@@ -20927,7 +20927,7 @@
       </c>
       <c r="F466" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G466" s="3" t="inlineStr">
@@ -20969,7 +20969,7 @@
       </c>
       <c r="F467" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G467" s="3" t="inlineStr">
@@ -21011,7 +21011,7 @@
       </c>
       <c r="F468" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G468" s="3" t="inlineStr">
@@ -21053,7 +21053,7 @@
       </c>
       <c r="F469" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G469" s="3" t="inlineStr">
@@ -21093,7 +21093,7 @@
       </c>
       <c r="F470" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G470" s="3" t="inlineStr">
@@ -21133,7 +21133,7 @@
       </c>
       <c r="F471" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G471" s="3" t="inlineStr">
@@ -21173,7 +21173,7 @@
       </c>
       <c r="F472" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G472" s="3" t="inlineStr">
@@ -21213,7 +21213,7 @@
       </c>
       <c r="F473" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G473" s="3" t="inlineStr">
@@ -21253,7 +21253,7 @@
       </c>
       <c r="F474" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G474" s="3" t="inlineStr">
@@ -21293,7 +21293,7 @@
       </c>
       <c r="F475" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G475" s="3" t="inlineStr">
@@ -21333,7 +21333,7 @@
       </c>
       <c r="F476" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G476" s="3" t="inlineStr">
@@ -21373,7 +21373,7 @@
       </c>
       <c r="F477" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G477" s="3" t="inlineStr">
@@ -21413,7 +21413,7 @@
       </c>
       <c r="F478" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G478" s="3" t="inlineStr">
@@ -21453,7 +21453,7 @@
       </c>
       <c r="F479" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G479" s="3" t="inlineStr">
@@ -21493,7 +21493,7 @@
       </c>
       <c r="F480" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G480" s="3" t="inlineStr">
@@ -21533,7 +21533,7 @@
       </c>
       <c r="F481" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G481" s="3" t="inlineStr">
@@ -21575,7 +21575,7 @@
       </c>
       <c r="F482" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G482" s="3" t="inlineStr">
@@ -21617,7 +21617,7 @@
       </c>
       <c r="F483" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G483" s="3" t="inlineStr">
@@ -21657,7 +21657,7 @@
       </c>
       <c r="F484" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G484" s="3" t="inlineStr">
@@ -21697,7 +21697,7 @@
       </c>
       <c r="F485" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G485" s="3" t="inlineStr">
@@ -21737,7 +21737,7 @@
       </c>
       <c r="F486" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G486" s="3" t="inlineStr">
@@ -21777,7 +21777,7 @@
       </c>
       <c r="F487" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G487" s="3" t="inlineStr">
@@ -21819,7 +21819,7 @@
       </c>
       <c r="F488" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G488" s="3" t="inlineStr">
@@ -21861,7 +21861,7 @@
       </c>
       <c r="F489" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G489" s="3" t="inlineStr">
@@ -21903,7 +21903,7 @@
       </c>
       <c r="F490" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G490" s="3" t="inlineStr">
@@ -21945,7 +21945,7 @@
       </c>
       <c r="F491" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G491" s="3" t="inlineStr">
@@ -21985,7 +21985,7 @@
       </c>
       <c r="F492" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G492" s="3" t="inlineStr">
@@ -22027,7 +22027,7 @@
       </c>
       <c r="F493" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G493" s="3" t="inlineStr">
@@ -22069,7 +22069,7 @@
       </c>
       <c r="F494" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G494" s="3" t="inlineStr">
@@ -22119,7 +22119,7 @@
       </c>
       <c r="F495" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G495" s="3" t="inlineStr">
@@ -22159,7 +22159,7 @@
       </c>
       <c r="F496" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G496" s="3" t="inlineStr">
@@ -22199,7 +22199,7 @@
       </c>
       <c r="F497" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G497" s="3" t="inlineStr">
@@ -22239,7 +22239,7 @@
       </c>
       <c r="F498" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G498" s="3" t="inlineStr">
@@ -22279,7 +22279,7 @@
       </c>
       <c r="F499" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G499" s="3" t="inlineStr">
@@ -22319,7 +22319,7 @@
       </c>
       <c r="F500" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G500" s="3" t="inlineStr">
@@ -22359,7 +22359,7 @@
       </c>
       <c r="F501" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G501" s="3" t="inlineStr">
@@ -22399,7 +22399,7 @@
       </c>
       <c r="F502" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G502" s="3" t="inlineStr">
@@ -22439,7 +22439,7 @@
       </c>
       <c r="F503" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G503" s="3" t="inlineStr">
@@ -22479,7 +22479,7 @@
       </c>
       <c r="F504" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G504" s="3" t="inlineStr">
@@ -22519,7 +22519,7 @@
       </c>
       <c r="F505" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G505" s="3" t="inlineStr">
@@ -22559,7 +22559,7 @@
       </c>
       <c r="F506" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G506" s="3" t="inlineStr">
@@ -22599,7 +22599,7 @@
       </c>
       <c r="F507" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G507" s="3" t="inlineStr">
@@ -22639,7 +22639,7 @@
       </c>
       <c r="F508" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G508" s="3" t="inlineStr">
@@ -22679,7 +22679,7 @@
       </c>
       <c r="F509" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G509" s="3" t="inlineStr">
@@ -22719,7 +22719,7 @@
       </c>
       <c r="F510" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G510" s="3" t="inlineStr">
@@ -22759,7 +22759,7 @@
       </c>
       <c r="F511" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G511" s="3" t="inlineStr">
@@ -22813,7 +22813,7 @@
       </c>
       <c r="F512" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G512" s="3" t="inlineStr">
@@ -22853,7 +22853,7 @@
       </c>
       <c r="F513" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G513" s="3" t="inlineStr">
@@ -22893,7 +22893,7 @@
       </c>
       <c r="F514" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G514" s="3" t="inlineStr">
@@ -22933,7 +22933,7 @@
       </c>
       <c r="F515" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G515" s="3" t="inlineStr">
@@ -22973,7 +22973,7 @@
       </c>
       <c r="F516" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G516" s="3" t="inlineStr">
@@ -23015,7 +23015,7 @@
       </c>
       <c r="F517" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G517" s="3" t="inlineStr">
@@ -23057,7 +23057,7 @@
       </c>
       <c r="F518" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G518" s="3" t="inlineStr">
@@ -23097,7 +23097,7 @@
       </c>
       <c r="F519" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G519" s="3" t="inlineStr">
@@ -23139,7 +23139,7 @@
       </c>
       <c r="F520" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G520" s="3" t="inlineStr">
@@ -23179,7 +23179,7 @@
       </c>
       <c r="F521" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G521" s="3" t="inlineStr">
@@ -23219,7 +23219,7 @@
       </c>
       <c r="F522" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G522" s="3" t="inlineStr">
@@ -23259,7 +23259,7 @@
       </c>
       <c r="F523" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G523" s="3" t="inlineStr">
@@ -23301,7 +23301,7 @@
       </c>
       <c r="F524" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G524" s="3" t="inlineStr">
@@ -23349,7 +23349,7 @@
       </c>
       <c r="F525" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G525" s="3" t="inlineStr">
@@ -23391,7 +23391,7 @@
       </c>
       <c r="F526" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G526" s="3" t="inlineStr">
@@ -23437,7 +23437,7 @@
       </c>
       <c r="F527" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G527" s="3" t="inlineStr">
@@ -23477,7 +23477,7 @@
       </c>
       <c r="F528" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G528" s="3" t="inlineStr">
@@ -23519,7 +23519,7 @@
       </c>
       <c r="F529" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G529" s="3" t="inlineStr">
@@ -23561,7 +23561,7 @@
       </c>
       <c r="F530" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G530" s="3" t="inlineStr">
@@ -23613,7 +23613,7 @@
       </c>
       <c r="F531" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G531" s="3" t="inlineStr">
@@ -23655,7 +23655,7 @@
       </c>
       <c r="F532" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G532" s="3" t="inlineStr">
@@ -23776,7 +23776,7 @@
       </c>
       <c r="F533" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G533" s="3" t="inlineStr">
@@ -23818,7 +23818,7 @@
       </c>
       <c r="F534" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G534" s="4" t="inlineStr">
@@ -23858,7 +23858,7 @@
       </c>
       <c r="F535" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G535" s="4" t="inlineStr">
@@ -23898,7 +23898,7 @@
       </c>
       <c r="F536" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G536" s="3" t="inlineStr">
@@ -23940,7 +23940,7 @@
       </c>
       <c r="F537" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G537" s="3" t="inlineStr">
@@ -23980,7 +23980,7 @@
       </c>
       <c r="F538" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G538" s="3" t="inlineStr">
@@ -24020,7 +24020,7 @@
       </c>
       <c r="F539" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G539" s="3" t="inlineStr">
@@ -24060,7 +24060,7 @@
       </c>
       <c r="F540" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G540" s="3" t="inlineStr">
@@ -24100,7 +24100,7 @@
       </c>
       <c r="F541" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G541" s="3" t="inlineStr">
@@ -24140,7 +24140,7 @@
       </c>
       <c r="F542" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G542" s="3" t="inlineStr">
@@ -24180,7 +24180,7 @@
       </c>
       <c r="F543" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G543" s="3" t="inlineStr">
@@ -24220,7 +24220,7 @@
       </c>
       <c r="F544" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G544" s="3" t="inlineStr">
@@ -24262,7 +24262,7 @@
       </c>
       <c r="F545" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G545" s="3" t="inlineStr">
@@ -24304,7 +24304,7 @@
       </c>
       <c r="F546" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G546" s="3" t="inlineStr">
@@ -24346,7 +24346,7 @@
       </c>
       <c r="F547" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G547" s="3" t="inlineStr">
@@ -24398,7 +24398,7 @@
       </c>
       <c r="F548" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G548" s="4" t="inlineStr">
@@ -24438,7 +24438,7 @@
       </c>
       <c r="F549" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G549" s="3" t="inlineStr">
@@ -24480,7 +24480,7 @@
       </c>
       <c r="F550" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G550" s="3" t="inlineStr">
@@ -24522,7 +24522,7 @@
       </c>
       <c r="F551" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G551" s="3" t="inlineStr">
@@ -24568,7 +24568,7 @@
       </c>
       <c r="F552" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G552" s="3" t="inlineStr">
@@ -24608,7 +24608,7 @@
       </c>
       <c r="F553" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G553" s="3" t="inlineStr">
@@ -24648,7 +24648,7 @@
       </c>
       <c r="F554" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G554" s="3" t="inlineStr">
@@ -24688,7 +24688,7 @@
       </c>
       <c r="F555" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G555" s="3" t="inlineStr">
@@ -24728,7 +24728,7 @@
       </c>
       <c r="F556" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G556" s="3" t="inlineStr">
@@ -24768,7 +24768,7 @@
       </c>
       <c r="F557" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G557" s="3" t="inlineStr">
@@ -24808,7 +24808,7 @@
       </c>
       <c r="F558" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G558" s="3" t="inlineStr">
@@ -24848,7 +24848,7 @@
       </c>
       <c r="F559" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G559" s="3" t="inlineStr">
@@ -24888,7 +24888,7 @@
       </c>
       <c r="F560" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G560" s="3" t="inlineStr">
@@ -24928,7 +24928,7 @@
       </c>
       <c r="F561" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G561" s="3" t="inlineStr">
@@ -24968,7 +24968,7 @@
       </c>
       <c r="F562" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G562" s="3" t="inlineStr">
@@ -25018,7 +25018,7 @@
       </c>
       <c r="F563" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G563" s="3" t="inlineStr">
@@ -25066,7 +25066,7 @@
       </c>
       <c r="F564" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G564" s="3" t="inlineStr">
@@ -25106,7 +25106,7 @@
       </c>
       <c r="F565" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G565" s="3" t="inlineStr">
@@ -25148,7 +25148,7 @@
       </c>
       <c r="F566" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G566" s="3" t="inlineStr">
@@ -25190,7 +25190,7 @@
       </c>
       <c r="F567" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G567" s="3" t="inlineStr">
@@ -25230,7 +25230,7 @@
       </c>
       <c r="F568" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G568" s="3" t="inlineStr">
@@ -25270,7 +25270,7 @@
       </c>
       <c r="F569" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G569" s="3" t="inlineStr">
@@ -25312,7 +25312,7 @@
       </c>
       <c r="F570" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G570" s="3" t="inlineStr">
@@ -25360,7 +25360,7 @@
       </c>
       <c r="F571" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G571" s="3" t="inlineStr">
@@ -25402,7 +25402,7 @@
       </c>
       <c r="F572" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G572" s="3" t="inlineStr">
@@ -25442,7 +25442,7 @@
       </c>
       <c r="F573" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G573" s="3" t="inlineStr">
@@ -25482,7 +25482,7 @@
       </c>
       <c r="F574" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G574" s="3" t="inlineStr">
@@ -25522,7 +25522,7 @@
       </c>
       <c r="F575" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G575" s="3" t="inlineStr">
@@ -25562,7 +25562,7 @@
       </c>
       <c r="F576" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G576" s="3" t="inlineStr">
@@ -25602,7 +25602,7 @@
       </c>
       <c r="F577" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G577" s="3" t="inlineStr">
@@ -25642,7 +25642,7 @@
       </c>
       <c r="F578" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G578" s="3" t="inlineStr">
@@ -25682,7 +25682,7 @@
       </c>
       <c r="F579" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G579" s="3" t="inlineStr">
@@ -25722,7 +25722,7 @@
       </c>
       <c r="F580" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G580" s="3" t="inlineStr">
@@ -25762,7 +25762,7 @@
       </c>
       <c r="F581" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G581" s="3" t="inlineStr">
@@ -25804,7 +25804,7 @@
       </c>
       <c r="F582" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G582" s="3" t="inlineStr">
@@ -25846,7 +25846,7 @@
       </c>
       <c r="F583" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G583" s="3" t="inlineStr">
@@ -25888,7 +25888,7 @@
       </c>
       <c r="F584" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G584" s="3" t="inlineStr">
@@ -25930,7 +25930,7 @@
       </c>
       <c r="F585" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G585" s="3" t="inlineStr">
@@ -25979,7 +25979,7 @@
       </c>
       <c r="F586" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G586" s="3" t="inlineStr">
@@ -26021,7 +26021,7 @@
       </c>
       <c r="F587" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G587" s="3" t="inlineStr">
@@ -26063,7 +26063,7 @@
       </c>
       <c r="F588" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G588" s="3" t="inlineStr">
@@ -26105,7 +26105,7 @@
       </c>
       <c r="F589" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G589" s="3" t="inlineStr">
@@ -26155,7 +26155,7 @@
       </c>
       <c r="F590" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G590" s="3" t="inlineStr">
@@ -26197,7 +26197,7 @@
       </c>
       <c r="F591" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G591" s="3" t="inlineStr">
@@ -26245,7 +26245,7 @@
       </c>
       <c r="F592" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G592" s="3" t="inlineStr">
@@ -26287,7 +26287,7 @@
       </c>
       <c r="F593" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G593" s="3" t="inlineStr">
@@ -26329,7 +26329,7 @@
       </c>
       <c r="F594" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G594" s="3" t="inlineStr">
@@ -26371,7 +26371,7 @@
       </c>
       <c r="F595" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G595" s="3" t="inlineStr">
@@ -26413,7 +26413,7 @@
       </c>
       <c r="F596" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G596" s="3" t="inlineStr">
@@ -26461,7 +26461,7 @@
       </c>
       <c r="F597" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G597" s="3" t="inlineStr">
@@ -26503,7 +26503,7 @@
       </c>
       <c r="F598" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G598" s="3" t="inlineStr">
@@ -26545,7 +26545,7 @@
       </c>
       <c r="F599" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G599" s="3" t="inlineStr">
@@ -26593,7 +26593,7 @@
       </c>
       <c r="F600" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G600" s="3" t="inlineStr">
@@ -26633,7 +26633,7 @@
       </c>
       <c r="F601" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G601" s="3" t="inlineStr">
@@ -26673,7 +26673,7 @@
       </c>
       <c r="F602" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G602" s="3" t="inlineStr">
@@ -26715,7 +26715,7 @@
       </c>
       <c r="F603" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G603" s="3" t="inlineStr">
@@ -26759,7 +26759,7 @@
       </c>
       <c r="F604" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G604" s="3" t="inlineStr">
@@ -26799,7 +26799,7 @@
       </c>
       <c r="F605" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G605" s="3" t="inlineStr">
@@ -26855,7 +26855,7 @@
       </c>
       <c r="F606" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G606" s="3" t="inlineStr">
